--- a/Electronics/GEO_GUESSER_PROJECT_Finale/Project Outputs for GEO_GUESSER_PROJECT_FINALE/BOM/Bill of Materials-GEO_GUESSER_PROJECT_FINALE.xlsx
+++ b/Electronics/GEO_GUESSER_PROJECT_Finale/Project Outputs for GEO_GUESSER_PROJECT_FINALE/BOM/Bill of Materials-GEO_GUESSER_PROJECT_FINALE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pghd3\Desktop\poli\SWDP\Project\Electronics\GEO_GUESSER_PROJECT_Finale\GEO_GUESSER_PROJECT_Finale\Project Outputs for GEO_GUESSER_PROJECT_FINALE\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pghd3\Desktop\poli\SWDP\Project\Electronics\GEO_GUESSER_PROJECT_FINALE\Project Outputs for GEO_GUESSER_PROJECT_FINALE\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C62870-CD35-4083-96D7-F20ABFD1B2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E08C3937-9D34-4B90-8F25-6517AA6EC52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{82592F46-CB44-44EE-8DA3-10C5E6299895}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{598A182F-0A23-4855-9BB4-3F36AE3C4D38}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-GEO_GUESSER_P" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
   <si>
     <t>Line #</t>
   </si>
@@ -575,7 +575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF421606-C995-4995-8D95-DD240A510629}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B05E510-7349-4098-9A88-6B25567146E1}">
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -661,14 +661,16 @@
         <v>13</v>
       </c>
       <c r="K2" s="1">
-        <v>2.2399999999999998E-3</v>
+        <v>4.8799999999999998E-3</v>
       </c>
       <c r="L2" s="1">
-        <v>22.44</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
@@ -735,14 +737,16 @@
         <v>13</v>
       </c>
       <c r="K4" s="1">
-        <v>4.1419999999999998E-2</v>
+        <v>4.1849999999999998E-2</v>
       </c>
       <c r="L4" s="1">
-        <v>8.2839999999999997E-2</v>
+        <v>8.3699999999999997E-2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
@@ -771,10 +775,10 @@
         <v>28</v>
       </c>
       <c r="K5" s="1">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="L5" s="1">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -809,14 +813,16 @@
         <v>29</v>
       </c>
       <c r="K6" s="1">
-        <v>5.1799999999999997E-3</v>
+        <v>5.2300000000000003E-3</v>
       </c>
       <c r="L6" s="1">
-        <v>1.0359999999999999E-2</v>
+        <v>1.0460000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
@@ -844,7 +850,9 @@
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
@@ -880,7 +888,9 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
